--- a/Data/EXCEL/Transfer/salemon/202507-1/912000-salemon-202507.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202507-1/912000-salemon-202507.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202507\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{327ADD51-35A8-4A6C-A2A5-6478053A36D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08AE5962-78F5-4C03-BE06-9AB1F2F58220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6180" yWindow="585" windowWidth="21750" windowHeight="13170" xr2:uid="{53114A42-F740-4F38-B324-25A78FB64E71}"/>
+    <workbookView xWindow="6525" yWindow="930" windowWidth="21750" windowHeight="13170" xr2:uid="{6A102209-8029-441D-BEB1-EA9328E28510}"/>
   </bookViews>
   <sheets>
     <sheet name="912000-salemon-202507" sheetId="2" r:id="rId1"/>
@@ -1255,7 +1255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1665502F-580B-4502-B4D9-E3B617521AA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1F44D8-ABC8-4CCD-B3D9-7339869AC0A8}">
   <dimension ref="A1:Q44"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
